--- a/templates/student_template.xlsx
+++ b/templates/student_template.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SRMS\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A37096-6B87-45A9-B575-78C242949A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
-  <si>
-    <t>Batch Year</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>Semester</t>
   </si>
@@ -38,21 +40,9 @@
     <t>Board Roll</t>
   </si>
   <si>
-    <t>CSE</t>
-  </si>
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>CSE-2025-001</t>
-  </si>
-  <si>
     <t>IDX2025001</t>
   </si>
   <si>
-    <t>BR20250001</t>
-  </si>
-  <si>
     <t>Jane Smith</t>
   </si>
   <si>
@@ -62,12 +52,6 @@
     <t>IDX2025002</t>
   </si>
   <si>
-    <t>BR20250002</t>
-  </si>
-  <si>
-    <t>EEE</t>
-  </si>
-  <si>
     <t>Mike Johnson</t>
   </si>
   <si>
@@ -80,9 +64,6 @@
     <t>BR20250003</t>
   </si>
   <si>
-    <t>ME</t>
-  </si>
-  <si>
     <t>Sarah Williams</t>
   </si>
   <si>
@@ -105,30 +86,44 @@
   </si>
   <si>
     <t>BR20250005</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
+    <t>19TH</t>
+  </si>
+  <si>
+    <t>pattia dio</t>
+  </si>
+  <si>
+    <t>cst-m-1915</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -153,14 +148,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -450,172 +453,224 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="G2">
+        <v>759291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G3">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2025</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2025</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="G6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>2025</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/templates/student_template.xlsx
+++ b/templates/student_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SRMS\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A37096-6B87-45A9-B575-78C242949A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D280D8A-F3AB-4F44-AB19-3F8BA6237850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>Semester</t>
   </si>
@@ -43,18 +43,12 @@
     <t>IDX2025001</t>
   </si>
   <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
     <t>CSE-2025-002</t>
   </si>
   <si>
     <t>IDX2025002</t>
   </si>
   <si>
-    <t>Mike Johnson</t>
-  </si>
-  <si>
     <t>EEE-2025-001</t>
   </si>
   <si>
@@ -64,9 +58,6 @@
     <t>BR20250003</t>
   </si>
   <si>
-    <t>Sarah Williams</t>
-  </si>
-  <si>
     <t>ME-2025-001</t>
   </si>
   <si>
@@ -76,9 +67,6 @@
     <t>BR20250004</t>
   </si>
   <si>
-    <t>David Brown</t>
-  </si>
-  <si>
     <t>CSE-2025-003</t>
   </si>
   <si>
@@ -104,6 +92,36 @@
   </si>
   <si>
     <t>cst-m-1915</t>
+  </si>
+  <si>
+    <t>abdur rahaman</t>
+  </si>
+  <si>
+    <t>saima satter</t>
+  </si>
+  <si>
+    <t>tammana naznim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sonjit chiran </t>
+  </si>
+  <si>
+    <t>mahamudur rahman</t>
+  </si>
+  <si>
+    <t>shanto chandra dey</t>
+  </si>
+  <si>
+    <t>mong chang sing marma</t>
+  </si>
+  <si>
+    <t>suchon b kha kha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kaji muntachir </t>
+  </si>
+  <si>
+    <t>jorge m. d silva</t>
   </si>
 </sst>
 </file>
@@ -467,7 +485,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -490,19 +508,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -513,22 +531,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
       </c>
       <c r="G3">
         <v>759</v>
@@ -536,137 +554,155 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/templates/student_template.xlsx
+++ b/templates/student_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SRMS\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D280D8A-F3AB-4F44-AB19-3F8BA6237850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1FB595-C1D8-4F1F-A410-19371263752B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11205" yWindow="2115" windowWidth="12045" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>Semester</t>
   </si>
   <si>
-    <t>Department</t>
-  </si>
-  <si>
     <t>Student Name</t>
   </si>
   <si>
@@ -40,88 +37,88 @@
     <t>Board Roll</t>
   </si>
   <si>
-    <t>IDX2025001</t>
-  </si>
-  <si>
-    <t>CSE-2025-002</t>
-  </si>
-  <si>
-    <t>IDX2025002</t>
-  </si>
-  <si>
-    <t>EEE-2025-001</t>
-  </si>
-  <si>
-    <t>IDX2025003</t>
-  </si>
-  <si>
-    <t>BR20250003</t>
-  </si>
-  <si>
-    <t>ME-2025-001</t>
-  </si>
-  <si>
-    <t>IDX2025004</t>
-  </si>
-  <si>
-    <t>BR20250004</t>
-  </si>
-  <si>
-    <t>CSE-2025-003</t>
-  </si>
-  <si>
-    <t>IDX2025005</t>
-  </si>
-  <si>
-    <t>BR20250005</t>
-  </si>
-  <si>
     <t>6th</t>
   </si>
   <si>
-    <t>CST</t>
-  </si>
-  <si>
     <t>Batch</t>
   </si>
   <si>
-    <t>19TH</t>
-  </si>
-  <si>
-    <t>pattia dio</t>
-  </si>
-  <si>
-    <t>cst-m-1915</t>
-  </si>
-  <si>
-    <t>abdur rahaman</t>
-  </si>
-  <si>
-    <t>saima satter</t>
-  </si>
-  <si>
-    <t>tammana naznim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sonjit chiran </t>
-  </si>
-  <si>
-    <t>mahamudur rahman</t>
-  </si>
-  <si>
-    <t>shanto chandra dey</t>
-  </si>
-  <si>
-    <t>mong chang sing marma</t>
-  </si>
-  <si>
-    <t>suchon b kha kha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kaji muntachir </t>
-  </si>
-  <si>
-    <t>jorge m. d silva</t>
+    <t xml:space="preserve">19th       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19th      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19th     </t>
+  </si>
+  <si>
+    <t>Patia Dio</t>
+  </si>
+  <si>
+    <t>Md.Abdur Rahman</t>
+  </si>
+  <si>
+    <t>Saima Akter</t>
+  </si>
+  <si>
+    <t>Tamanna Naznin</t>
+  </si>
+  <si>
+    <t>Sonjit Chiran</t>
+  </si>
+  <si>
+    <t>Md.Mahamudur Rahman</t>
+  </si>
+  <si>
+    <t>Shanto Chandra Dey</t>
+  </si>
+  <si>
+    <t>Mong Chaing Sing Marma</t>
+  </si>
+  <si>
+    <t>Benedicta Kha Kha</t>
+  </si>
+  <si>
+    <t>Kazi Muntasir Hossain</t>
+  </si>
+  <si>
+    <t>Jorge Martin D Silva</t>
+  </si>
+  <si>
+    <t>CST-22-M1920</t>
+  </si>
+  <si>
+    <t>CST-22-M1925</t>
+  </si>
+  <si>
+    <t>CST-22-M1910</t>
+  </si>
+  <si>
+    <t>CST-22-M1913</t>
+  </si>
+  <si>
+    <t>CST-22-M1911</t>
+  </si>
+  <si>
+    <t>CST-22-M1914</t>
+  </si>
+  <si>
+    <t>CST-22-M1921</t>
+  </si>
+  <si>
+    <t>CST-22-M1902</t>
+  </si>
+  <si>
+    <t>CST-22-M1916</t>
+  </si>
+  <si>
+    <t>CST-22-M1901</t>
+  </si>
+  <si>
+    <t>Department Code</t>
+  </si>
+  <si>
+    <t>CST-22-M1917</t>
   </si>
 </sst>
 </file>
@@ -165,9 +162,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,232 +485,264 @@
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>85</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2">
+        <v>759278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G3" s="2">
+        <v>759279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>85</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2">
+        <v>759283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>85</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2">
+        <v>759284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>85</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2">
+        <v>759285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>85</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2">
+        <v>759287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>85</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="2">
+        <v>759291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>85</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2">
+        <v>759293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>85</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2">
+        <v>759296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>85</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>759291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E11" s="4"/>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2">
+        <v>759302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>85</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
+      <c r="G12" s="2">
+        <v>759305</v>
       </c>
     </row>
   </sheetData>
